--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_198_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_198_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9611</v>
+        <v>3.0231</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8073</v>
+        <v>1.8021</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1538</v>
+        <v>1.221</v>
       </c>
       <c r="G2" t="n">
         <v>1.6781</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1902</v>
+        <v>1.2522</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4327</v>
+        <v>1.4275</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2425</v>
+        <v>-0.1753</v>
       </c>
       <c r="V2" t="n">
         <v>0.7886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4503</v>
+        <v>2.8646</v>
       </c>
       <c r="E3" t="n">
-        <v>1.59</v>
+        <v>2.1222</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8602</v>
+        <v>0.7423</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6959</v>
+        <v>0.5893</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1237</v>
+        <v>0.6196</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5722</v>
+        <v>-0.0303</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4995</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8739</v>
+        <v>0.9278</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6257</v>
+        <v>-0.2378</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1963</v>
+        <v>-0.1007</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2499</v>
+        <v>-0.3082</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0535</v>
+        <v>0.2075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4323</v>
+        <v>0.3086</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0905</v>
+        <v>0.6253</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3418</v>
+        <v>-0.3167</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1418</v>
+        <v>3.3584</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2108</v>
+        <v>2.4681</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4622</v>
+        <v>1.9439</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7486</v>
+        <v>0.5242</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0908</v>
+        <v>1.6959</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9604</v>
+        <v>1.1237</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1304</v>
+        <v>0.5722</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5553</v>
+        <v>1.4995</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6827</v>
+        <v>0.8739</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1274</v>
+        <v>0.6257</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5355</v>
+        <v>0.1963</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2778</v>
+        <v>0.2499</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2578</v>
+        <v>-0.0535</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.871</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2951</v>
+        <v>0.4501</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5613</v>
+        <v>0.4443</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2662</v>
+        <v>0.0057</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1444</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0351</v>
+        <v>1.6882</v>
       </c>
       <c r="E5" t="n">
-        <v>0.609</v>
+        <v>-0.1276</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4261</v>
+        <v>1.8158</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1758</v>
+        <v>1.0908</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0156</v>
+        <v>0.9604</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8399</v>
+        <v>0.1304</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5798</v>
+        <v>0.5553</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6301</v>
+        <v>0.6827</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0502</v>
+        <v>-0.1274</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.404</v>
+        <v>0.5355</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3856</v>
+        <v>0.2778</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7896</v>
+        <v>0.2578</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-4.871</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8593</v>
+        <v>0.7725</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.9715</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6704</v>
+        <v>-0.199</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7028</v>
+        <v>1.2779</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2966</v>
+        <v>0.2551</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4063</v>
+        <v>1.0228</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5893</v>
+        <v>1.1758</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6196</v>
+        <v>2.0156</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0303</v>
+        <v>-0.8399</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.5798</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9278</v>
+        <v>1.6301</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2378</v>
+        <v>-0.0502</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1007</v>
+        <v>-0.404</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3082</v>
+        <v>0.3856</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2075</v>
+        <v>-0.7896</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8531</v>
+        <v>0.1021</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2003</v>
+        <v>-0.165</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6528</v>
+        <v>0.2671</v>
       </c>
       <c r="V6" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.323</v>
+        <v>0.5088</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7944</v>
+        <v>1.1482</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4714</v>
+        <v>-0.6394</v>
       </c>
       <c r="G7" t="n">
         <v>1.4638</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4424</v>
+        <v>-0.2566</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4991</v>
+        <v>-0.1452</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0567</v>
+        <v>-0.1114</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9304</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5721</v>
+        <v>-1.4706</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8381</v>
+        <v>-2.6022</v>
       </c>
       <c r="F8" t="n">
-        <v>1.266</v>
+        <v>1.1315</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4692</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4332</v>
+        <v>0.5346</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1968</v>
+        <v>0.4327</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2364</v>
+        <v>0.1019</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6784</v>
+        <v>-1.4889</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-1.7408</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9429999999999999</v>
+        <v>0.2519</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1363</v>
+        <v>-1.5725</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4801</v>
+        <v>-0.4081</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6562</v>
+        <v>-1.1644</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5351</v>
+        <v>-1.7764</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0672</v>
+        <v>-1.4551</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.3213</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6012</v>
+        <v>0.2039</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5473</v>
+        <v>1.047</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0539</v>
+        <v>-0.8431</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5601</v>
+        <v>0.228</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2003</v>
+        <v>0.2675</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3598</v>
+        <v>-0.0395</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3311</v>
+        <v>-1.5104</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4485</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1175</v>
+        <v>-0.775</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5725</v>
+        <v>-2.1363</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4081</v>
+        <v>-0.4801</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1644</v>
+        <v>-1.6562</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7764</v>
+        <v>-0.5351</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4551</v>
+        <v>0.0672</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3213</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2039</v>
+        <v>-1.6012</v>
       </c>
       <c r="N10" t="n">
-        <v>1.047</v>
+        <v>-0.5473</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8431</v>
+        <v>-1.0539</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6141</v>
+        <v>-0.3921</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4402</v>
+        <v>-0.2003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.174</v>
+        <v>-0.1918</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9577</v>
+        <v>-3.217</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6896</v>
+        <v>-1.2178</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.268</v>
+        <v>-1.9991</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1423</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0473</v>
+        <v>-0.3066</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>-0.1177</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4577</v>
+        <v>-0.1889</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.143800000000001</v>
+        <v>4.143800000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8479000000000005</v>
+        <v>0.8477000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>3.296099999999999</v>
+        <v>3.295999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3734</v>
+        <v>1.373399999999999</v>
       </c>
       <c r="H12" t="n">
         <v>5.2887</v>
@@ -1363,25 +1363,25 @@
         <v>-3.9154</v>
       </c>
       <c r="J12" t="n">
-        <v>5.218499999999999</v>
+        <v>5.2185</v>
       </c>
       <c r="K12" t="n">
-        <v>4.902</v>
+        <v>4.901999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3166000000000002</v>
+        <v>0.3166</v>
       </c>
       <c r="M12" t="n">
         <v>-3.8452</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3869</v>
+        <v>0.3868999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-4.2319</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3195</v>
+        <v>-2.319500000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.2368</v>
@@ -1390,13 +1390,13 @@
         <v>13.9173</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6931</v>
+        <v>2.6928</v>
       </c>
       <c r="T12" t="n">
-        <v>3.540800000000001</v>
+        <v>3.5406</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8476999999999999</v>
+        <v>-0.8479000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>2.3969</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4591</v>
+        <v>4.4818</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9509</v>
+        <v>3.5355</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5081</v>
+        <v>0.9463</v>
       </c>
       <c r="G13" t="n">
         <v>5.0351</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1715</v>
+        <v>1.1942</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3318</v>
+        <v>0.9164</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1603</v>
+        <v>0.2779</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8197</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1035</v>
+        <v>3.5788</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7301</v>
+        <v>1.0111</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6266</v>
+        <v>2.5677</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4608</v>
+        <v>2.4997</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2854</v>
+        <v>0.0203</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1754</v>
+        <v>2.4794</v>
       </c>
       <c r="J14" t="n">
-        <v>4.922</v>
+        <v>2.2384</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2119</v>
+        <v>-0.0399</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7101</v>
+        <v>2.2784</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4612</v>
+        <v>0.2612</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9265</v>
+        <v>0.0602</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4653</v>
+        <v>0.201</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8556</v>
+        <v>3.2473</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2851</v>
+        <v>0.1513</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4086</v>
+        <v>0.02</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1235</v>
+        <v>0.1314</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0569</v>
+        <v>2.8791</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1855</v>
+        <v>3.2019</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8714</v>
+        <v>-0.3228</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4997</v>
+        <v>4.4608</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0203</v>
+        <v>1.2854</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4794</v>
+        <v>3.1754</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2384</v>
+        <v>4.922</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0399</v>
+        <v>2.2119</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2784</v>
+        <v>2.7101</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2612</v>
+        <v>-0.4612</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0602</v>
+        <v>-0.9265</v>
       </c>
       <c r="O15" t="n">
-        <v>0.201</v>
+        <v>0.4653</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2473</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3706</v>
+        <v>0.4905</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8057</v>
+        <v>0.0633</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5649</v>
+        <v>0.4272</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.0203</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1705</v>
+        <v>-0.0983</v>
       </c>
       <c r="G16" t="n">
         <v>0.4533</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5764</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0562</v>
+        <v>-0.2126</v>
       </c>
       <c r="V16" t="n">
         <v>1.3558</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.342</v>
+        <v>-0.1848</v>
       </c>
       <c r="E17" t="n">
         <v>0.1941</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5361</v>
+        <v>-0.3788</v>
       </c>
       <c r="G17" t="n">
         <v>-0.342</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1573</v>
       </c>
       <c r="T17" t="n">
         <v>0.1573</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1573</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.344</v>
+        <v>-0.3833</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8528</v>
+        <v>-1.2066</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5087</v>
+        <v>0.8233</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0399</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4639</v>
+        <v>0.4246</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5623</v>
+        <v>0.2084</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0984</v>
+        <v>0.2161</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1668</v>
+        <v>-1.1332</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0104</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1564</v>
+        <v>-0.1228</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8079</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3589</v>
+        <v>-0.3253</v>
       </c>
       <c r="T19" t="n">
         <v>-0.224</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0015</v>
+        <v>-1.4723</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6207</v>
+        <v>-1.2698</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3809</v>
+        <v>-0.2024</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.0281</v>
+        <v>-0.9316</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.6902</v>
+        <v>-0.6037</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3379</v>
+        <v>-0.3279</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.6739</v>
+        <v>-0.3346</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.7637</v>
+        <v>-0.0133</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9102</v>
+        <v>-0.3213</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3542</v>
+        <v>-0.5969</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9265</v>
+        <v>-0.5904</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5723</v>
+        <v>-0.0065</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7389</v>
+        <v>-0.002</v>
       </c>
       <c r="T20" t="n">
-        <v>0.767</v>
+        <v>0.0828</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5059</v>
+        <v>-0.0848</v>
       </c>
       <c r="V20" t="n">
-        <v>1.214</v>
+        <v>-1.4665</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2862</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7583</v>
+        <v>-1.7048</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8596</v>
+        <v>-1.9745</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8987000000000001</v>
+        <v>0.2697</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9316</v>
+        <v>-5.0281</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6037</v>
+        <v>-4.6902</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3279</v>
+        <v>-0.3379</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3346</v>
+        <v>-4.6739</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0133</v>
+        <v>-3.7637</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3213</v>
+        <v>-0.9102</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5969</v>
+        <v>-0.3542</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5904</v>
+        <v>-0.9265</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0065</v>
+        <v>0.5723</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.288</v>
+        <v>-0.4422</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.507</v>
+        <v>0.4132</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7811</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4665</v>
+        <v>1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>2.2862</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9493</v>
+        <v>-2.6063</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5904</v>
+        <v>-2.2366</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3589</v>
+        <v>-0.3697</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9709</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0215</v>
+        <v>0.3646</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3576</v>
+        <v>-0.0037</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3791</v>
+        <v>0.3684</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.274</v>
+        <v>-4.3755</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3251</v>
+        <v>-3.561</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9489</v>
+        <v>-0.8145</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7019</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7319</v>
+        <v>-0.8334</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0351</v>
+        <v>-0.2711</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6967</v>
+        <v>-0.5623</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.143500000000001</v>
+        <v>-0.9984999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-3.295999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8478</v>
+        <v>2.2977</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.373400000000002</v>
+        <v>-1.373400000000003</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.288799999999998</v>
+        <v>-5.2888</v>
       </c>
       <c r="I24" t="n">
-        <v>3.915400000000001</v>
+        <v>3.915399999999999</v>
       </c>
       <c r="J24" t="n">
         <v>3.8451</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3866999999999998</v>
+        <v>-0.3867000000000007</v>
       </c>
       <c r="L24" t="n">
         <v>4.232100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>16.2367</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.6929</v>
+        <v>0.4523</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8478</v>
+        <v>0.8480000000000002</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5407</v>
+        <v>-0.3952999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3969</v>
